--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -663,19 +663,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -694,29 +694,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -735,29 +735,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -776,29 +776,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -858,29 +858,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1073,19 +1073,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1309,29 +1309,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1350,29 +1350,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1442,29 +1442,29 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44408</v>
+        <v>44742</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,61 +2949,143 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>60</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
         <v>59</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F65" s="1" t="n">
         <v>44439</v>
       </c>
-      <c r="G63" s="1" t="n">
+      <c r="G65" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -1391,13 +1391,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,7 +1290,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,19 +1360,19 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1442,29 +1442,29 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44742</v>
+        <v>44408</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,29 +2949,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,102 +2990,20 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>60</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>44408</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>59</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,7 +1290,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,19 +1360,19 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1442,29 +1442,29 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44408</v>
+        <v>44742</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,61 +2949,143 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>60</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
         <v>59</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F65" s="1" t="n">
         <v>44439</v>
       </c>
-      <c r="G63" s="1" t="n">
+      <c r="G65" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,7 +798,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -868,19 +868,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1073,19 +1073,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,19 +1360,19 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1442,29 +1442,29 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44742</v>
+        <v>44408</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,29 +2949,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,102 +2990,20 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>60</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>44408</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>59</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,7 +798,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -868,19 +868,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1073,19 +1073,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,19 +1360,19 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1442,29 +1442,29 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44408</v>
+        <v>44742</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,61 +2949,143 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>60</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
         <v>59</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F65" s="1" t="n">
         <v>44439</v>
       </c>
-      <c r="G63" s="1" t="n">
+      <c r="G65" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -571,13 +571,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2684,7 +2684,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,29 +2949,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,102 +2990,20 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>60</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>44408</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>59</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2684,7 +2684,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,61 +2949,143 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>60</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
         <v>59</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F65" s="1" t="n">
         <v>44439</v>
       </c>
-      <c r="G63" s="1" t="n">
+      <c r="G65" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -530,29 +530,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>atividade</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -571,29 +571,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atividade</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -612,29 +612,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -653,29 +653,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -694,29 +694,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -735,29 +735,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -776,29 +776,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -858,29 +858,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1073,19 +1073,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,19 +1360,19 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1442,29 +1442,29 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44742</v>
+        <v>44408</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,29 +2949,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,102 +2990,20 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>60</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>44408</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>59</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -530,29 +530,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>atividade</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -571,29 +571,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>atividade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -612,29 +612,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -653,29 +653,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -694,29 +694,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -735,29 +735,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -776,29 +776,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -858,29 +858,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1073,19 +1073,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,19 +1360,19 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1442,29 +1442,29 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44408</v>
+        <v>44742</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,61 +2949,143 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>60</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
         <v>59</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F65" s="1" t="n">
         <v>44439</v>
       </c>
-      <c r="G63" s="1" t="n">
+      <c r="G65" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -530,29 +530,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>atividade</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -571,29 +571,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atividade</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -612,29 +612,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -653,29 +653,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -694,29 +694,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -735,29 +735,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -776,29 +776,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -858,29 +858,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1186,29 +1186,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,29 +1360,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1391,39 +1391,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,39 +1432,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44742</v>
+        <v>44408</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44742</v>
+        <v>44408</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,29 +1842,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,29 +2416,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2457,29 +2457,29 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,39 +2498,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2539,39 +2539,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2580,39 +2580,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2621,39 +2621,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2713,19 +2713,19 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2744,29 +2744,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2826,266 +2826,20 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_selic_over</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>60</v>
-      </c>
-      <c r="F60" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>bcb_sgs_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>59</v>
-      </c>
-      <c r="F61" s="1" t="n">
-        <v>44408</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>46173</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>bcb_sgs_selic_meta</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>61</v>
-      </c>
-      <c r="F62" s="1" t="n">
-        <v>44408</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>bcb_sgs_selic_over</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>61</v>
-      </c>
-      <c r="F63" s="1" t="n">
-        <v>44408</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>60</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>44408</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>59</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -530,29 +530,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>atividade</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -571,29 +571,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>atividade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -612,29 +612,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -653,29 +653,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -694,29 +694,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -735,29 +735,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -776,29 +776,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -817,29 +817,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -861,26 +861,26 @@
         <v>59</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -981,29 +981,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,29 +1022,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1186,29 +1186,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1237,19 +1237,19 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1278,19 +1278,19 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,29 +1360,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1391,39 +1391,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,29 +1432,29 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44408</v>
+        <v>44742</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1483,19 +1483,19 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1524,19 +1524,19 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,29 +1842,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1934,19 +1934,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1975,19 +1975,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,29 +2416,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2457,29 +2457,29 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2508,29 +2508,29 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2539,39 +2539,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2580,29 +2580,29 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2621,29 +2621,29 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2744,29 +2744,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2788,26 +2788,26 @@
         <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2826,20 +2826,184 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_meta</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>61</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G60" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>61</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>60</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>59</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>atividade</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -489,29 +489,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>atividade</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -530,29 +530,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>atividade</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -571,29 +571,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atividade</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -612,29 +612,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46173</v>
+        <v>46234</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -653,29 +653,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -694,29 +694,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -735,29 +735,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -779,26 +779,26 @@
         <v>60</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -817,29 +817,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -858,29 +858,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -909,19 +909,19 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,29 +1022,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1114,19 +1114,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1186,29 +1186,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>44439</v>
+        <v>44742</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1237,19 +1237,19 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1278,19 +1278,19 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,29 +1360,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1391,39 +1391,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,29 +1432,29 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44742</v>
+        <v>44439</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1473,29 +1473,29 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1637,29 +1637,29 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1678,29 +1678,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1719,29 +1719,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1760,29 +1760,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1801,29 +1801,29 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,29 +1842,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2088,29 +2088,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2129,29 +2129,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2170,29 +2170,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2211,29 +2211,29 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2252,29 +2252,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2334,29 +2334,29 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2375,29 +2375,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,29 +2416,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,39 +2498,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2539,39 +2539,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2580,29 +2580,29 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2621,29 +2621,29 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2672,19 +2672,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2706,26 +2706,26 @@
         <v>59</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2747,26 +2747,26 @@
         <v>60</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2829,26 +2829,26 @@
         <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2908,102 +2908,20 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>60</v>
-      </c>
-      <c r="F62" s="1" t="n">
-        <v>44408</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>59</v>
-      </c>
-      <c r="F63" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>atividade</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -489,29 +489,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_ibc_br.csv</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_ibc_br.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>atividade</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -530,29 +530,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>atividade</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -571,29 +571,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>atividade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -612,29 +612,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46234</v>
+        <v>46173</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -653,29 +653,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -694,29 +694,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,26 +738,26 @@
         <v>59</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -776,29 +776,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -817,29 +817,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -858,29 +858,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -940,29 +940,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -981,29 +981,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1073,19 +1073,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1114,19 +1114,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1186,29 +1186,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44742</v>
+        <v>44469</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1312,26 +1312,26 @@
         <v>60</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1353,36 +1353,36 @@
         <v>49</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1391,39 +1391,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,39 +1432,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44439</v>
+        <v>44773</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44439</v>
+        <v>44773</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1555,29 +1555,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1599,26 +1599,26 @@
         <v>61</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>44408</v>
+        <v>44439</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2006,29 +2006,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2050,26 +2050,26 @@
         <v>60</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2293,29 +2293,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,29 +2416,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2457,29 +2457,29 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,39 +2498,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2539,39 +2539,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2580,39 +2580,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2621,39 +2621,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F54" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2672,19 +2672,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2744,29 +2744,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2829,26 +2829,26 @@
         <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44408</v>
+        <v>44469</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2918,10 +2918,174 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_meta</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>61</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>60</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>59</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>58</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1085,7 +1085,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1114,19 +1114,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1309,29 +1309,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1350,29 +1350,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1442,29 +1442,29 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44773</v>
+        <v>44439</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1719,29 +1719,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1801,29 +1801,29 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,29 +1842,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1968,26 +1968,26 @@
         <v>60</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2170,29 +2170,29 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F43" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2252,29 +2252,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2293,29 +2293,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F46" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2334,29 +2334,29 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F47" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,29 +2416,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2744,29 +2744,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,29 +2949,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,102 +2990,20 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>59</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>58</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -530,29 +530,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>atividade</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -571,29 +571,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atividade</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -612,29 +612,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -656,26 +656,26 @@
         <v>60</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -697,26 +697,26 @@
         <v>60</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -735,29 +735,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -776,29 +776,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -858,29 +858,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1186,29 +1186,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,29 +1360,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1391,39 +1391,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,29 +1432,29 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44773</v>
+        <v>44439</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1473,29 +1473,29 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1524,19 +1524,19 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1555,29 +1555,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1596,29 +1596,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1637,29 +1637,29 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1678,29 +1678,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1760,29 +1760,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1801,29 +1801,29 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,29 +1842,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1975,19 +1975,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2088,29 +2088,29 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2129,29 +2129,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2337,26 +2337,26 @@
         <v>60</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2375,29 +2375,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,39 +2416,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2457,39 +2457,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2501,36 +2501,36 @@
         <v>60</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2539,39 +2539,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2583,26 +2583,26 @@
         <v>60</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2624,26 +2624,26 @@
         <v>60</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2665,26 +2665,26 @@
         <v>59</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2744,29 +2744,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2829,181 +2829,17 @@
         <v>59</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>bcb_sgs_selic_meta</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>61</v>
-      </c>
-      <c r="F60" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>bcb_sgs_selic_over</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>60</v>
-      </c>
-      <c r="F61" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>59</v>
-      </c>
-      <c r="F62" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>58</v>
-      </c>
-      <c r="F63" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
+          <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -530,29 +530,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
+          <t>data/final/series/bcb_sgs_ibc_br_sa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>atividade</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -571,29 +571,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.csv</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cambio</t>
+          <t>atividade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -612,29 +612,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.csv</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_ibc_br_sa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1114,19 +1114,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1186,29 +1186,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,29 +1360,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1391,39 +1391,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,29 +1432,29 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44439</v>
+        <v>44773</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1483,19 +1483,19 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1524,19 +1524,19 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1596,29 +1596,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1801,29 +1801,29 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,29 +1842,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1934,19 +1934,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1975,19 +1975,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2006,29 +2006,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F39" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2211,29 +2211,29 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2337,26 +2337,26 @@
         <v>60</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2375,29 +2375,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,39 +2416,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2457,39 +2457,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2498,39 +2498,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2539,39 +2539,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2580,29 +2580,29 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2621,29 +2621,29 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2744,29 +2744,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2788,26 +2788,26 @@
         <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2829,17 +2829,181 @@
         <v>59</v>
       </c>
       <c r="F59" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_meta</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>61</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G60" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>61</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>60</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>59</v>
+      </c>
+      <c r="F63" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="G59" s="1" t="n">
+      <c r="G63" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -663,19 +663,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
+          <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -694,29 +694,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
+          <t>data/final/series/bcb_sgs_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -735,29 +735,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.csv</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_compra_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>cambio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -776,29 +776,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.csv</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_cambio_venda_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -858,29 +858,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1073,19 +1073,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,29 +1360,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1391,39 +1391,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,29 +1432,29 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44773</v>
+        <v>44439</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1483,19 +1483,19 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1524,19 +1524,19 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,29 +1842,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1934,19 +1934,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1975,19 +1975,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,29 +2416,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2457,29 +2457,29 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2508,29 +2508,29 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2549,29 +2549,29 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2580,29 +2580,29 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2621,29 +2621,29 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2672,19 +2672,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2744,29 +2744,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2788,26 +2788,26 @@
         <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2829,181 +2829,17 @@
         <v>59</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>bcb_sgs_selic_meta</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>61</v>
-      </c>
-      <c r="F60" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>bcb_sgs_selic_over</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>61</v>
-      </c>
-      <c r="F61" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>60</v>
-      </c>
-      <c r="F62" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>59</v>
-      </c>
-      <c r="F63" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1085,7 +1085,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1114,19 +1114,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1309,29 +1309,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1350,39 +1350,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1391,39 +1391,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,39 +1432,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44439</v>
+        <v>44773</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44439</v>
+        <v>44773</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,29 +1842,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,29 +2416,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2457,29 +2457,29 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,39 +2498,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2539,39 +2539,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2580,39 +2580,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2621,39 +2621,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2744,29 +2744,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2826,20 +2826,266 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G59" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>60</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G60" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bcb_sgs_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>59</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_meta</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>61</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>60</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G64" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>59</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1391,13 +1391,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,29 +2949,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,102 +2990,20 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>60</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>59</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,7 +798,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -858,29 +858,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,29 +1022,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1186,29 +1186,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,29 +1360,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1391,39 +1391,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,39 +1432,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44773</v>
+        <v>44439</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44773</v>
+        <v>44439</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,29 +1842,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,29 +2416,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2457,29 +2457,29 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,39 +2498,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2549,29 +2549,29 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2580,39 +2580,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2672,19 +2672,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2744,266 +2744,20 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>58</v>
-      </c>
-      <c r="F58" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_selic_over</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>60</v>
-      </c>
-      <c r="F59" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>bcb_sgs_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>59</v>
-      </c>
-      <c r="F60" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>bcb_sgs_selic_over</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>politica_monetaria</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>61</v>
-      </c>
-      <c r="F61" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>60</v>
-      </c>
-      <c r="F62" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>59</v>
-      </c>
-      <c r="F63" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,7 +798,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -827,19 +827,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -858,29 +858,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,29 +1022,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1186,29 +1186,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44773</v>
+        <v>44469</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1360,29 +1360,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1391,39 +1391,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,39 +1432,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44439</v>
+        <v>44773</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44439</v>
+        <v>44773</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1842,29 +1842,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1883,29 +1883,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2416,29 +2416,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2457,29 +2457,29 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,39 +2498,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2549,29 +2549,29 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2580,39 +2580,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2672,19 +2672,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2744,20 +2744,348 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G57" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>58</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G58" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>60</v>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G59" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>60</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G60" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bcb_sgs_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>59</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G61" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_meta</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>61</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>60</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G64" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>59</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -571,13 +571,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44439</v>
+        <v>46265</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46265</v>
@@ -2397,7 +2397,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2508,19 +2508,19 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,19 +2590,19 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2672,19 +2672,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2744,29 +2744,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2959,19 +2959,19 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,29 +2990,29 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3031,61 +3031,20 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G64" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>59</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>46265</v>
+        <v>44439</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46265</v>
@@ -2397,7 +2397,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2508,19 +2508,19 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,19 +2590,19 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2672,19 +2672,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2744,29 +2744,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2959,19 +2959,19 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,29 +2990,29 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3031,20 +3031,61 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G64" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>59</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2848,7 +2848,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,29 +2949,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,102 +2990,20 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>60</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>59</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2848,7 +2848,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,61 +2949,143 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>60</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
         <v>59</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F65" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="G63" s="1" t="n">
+      <c r="G65" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -981,13 +981,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1022,13 +1022,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1186,13 +1186,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1268,13 +1268,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2785,13 +2785,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2908,13 +2908,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2766,7 +2766,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,29 +2949,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,102 +2990,20 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>60</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>59</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2766,7 +2766,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,61 +2949,143 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>60</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
         <v>59</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F65" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="G63" s="1" t="n">
+      <c r="G65" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -880,7 +880,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -950,19 +950,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1032,19 +1032,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1073,19 +1073,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1104,29 +1104,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1145,29 +1145,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>credito</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44469</v>
+        <v>44773</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1309,29 +1309,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1350,29 +1350,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1401,19 +1401,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1442,29 +1442,29 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44773</v>
+        <v>44439</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1565,19 +1565,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1770,19 +1770,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2829,26 +2829,26 @@
         <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,29 +2949,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,102 +2990,20 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>60</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>59</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>46203</v>
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>46203</v>
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>46203</v>
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>46203</v>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>46265</v>
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>46265</v>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>46265</v>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>46265</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>46234</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>46234</v>
@@ -880,7 +880,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -899,29 +899,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44439</v>
+        <v>44500</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -940,29 +940,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.csv</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -981,29 +981,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.csv</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_pj</t>
+          <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1022,29 +1022,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.csv</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_inadimplencia_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcb_sgs_saldo_credito_total</t>
+          <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+          <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1114,19 +1114,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
+          <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
+          <t>data/final/series/bcb_sgs_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_saldo_credito_total</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1186,29 +1186,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.csv</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pf.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1227,29 +1227,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44439</v>
+        <v>44500</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.csv</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_pj.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
+          <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>inflacao</t>
+          <t>credito</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1268,29 +1268,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44773</v>
+        <v>44500</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.csv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_var_pct_saldo_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc</t>
+          <t>bcb_sgs_igp_m</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1312,26 +1312,26 @@
         <v>60</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m.csv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bcb_sgs_inpc_acum_12m</t>
+          <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1353,26 +1353,26 @@
         <v>49</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.csv</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_igp_m_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1391,29 +1391,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.csv</t>
+          <t>data/final/series/bcb_sgs_inpc.csv</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcb_sgs_ipca_acum_12m</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1432,39 +1432,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="G25" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.csv</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
+          <t>data/final/series/bcb_sgs_inpc_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yahoo_bova11</t>
+          <t>bcb_sgs_ipca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1473,39 +1473,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.csv</t>
+          <t>data/final/series/bcb_sgs_ipca.csv</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_bova11.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yahoo_dolar_real</t>
+          <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>inflacao</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1514,29 +1514,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44439</v>
+        <v>44804</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.csv</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.csv</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dolar_real.xlsx</t>
+          <t>data/final/series/bcb_sgs_ipca_acum_12m.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yahoo_dow_jones</t>
+          <t>yahoo_bova11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1558,26 +1558,26 @@
         <v>61</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.csv</t>
+          <t>data/final/series/yahoo_bova11.csv</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yahoo_euro_real</t>
+          <t>yahoo_dolar_real</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1599,26 +1599,26 @@
         <v>61</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.csv</t>
+          <t>data/final/series/yahoo_dolar_real.csv</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yahoo_ibovespa</t>
+          <t>yahoo_dow_jones</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1640,26 +1640,26 @@
         <v>61</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.csv</t>
+          <t>data/final/series/yahoo_dow_jones.csv</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>yahoo_ivvb11</t>
+          <t>yahoo_euro_real</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1681,26 +1681,26 @@
         <v>61</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.csv</t>
+          <t>data/final/series/yahoo_euro_real.csv</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_ibovespa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1722,26 +1722,26 @@
         <v>61</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_ibovespa.csv</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_ivvb11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1763,26 +1763,26 @@
         <v>61</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ivvb11.csv</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1804,26 +1804,26 @@
         <v>61</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1845,26 +1845,26 @@
         <v>61</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1886,26 +1886,26 @@
         <v>61</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1924,29 +1924,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2009,26 +2009,26 @@
         <v>60</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2050,26 +2050,26 @@
         <v>60</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2091,26 +2091,26 @@
         <v>60</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2132,26 +2132,26 @@
         <v>60</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2173,26 +2173,26 @@
         <v>60</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2214,26 +2214,26 @@
         <v>60</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2255,26 +2255,26 @@
         <v>60</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2296,26 +2296,26 @@
         <v>60</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2337,26 +2337,26 @@
         <v>60</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2378,26 +2378,26 @@
         <v>60</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2419,26 +2419,26 @@
         <v>60</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2460,26 +2460,26 @@
         <v>60</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44439</v>
+        <v>44500</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44439</v>
+        <v>44500</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2583,36 +2583,36 @@
         <v>61</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2624,36 +2624,36 @@
         <v>61</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F55" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2744,29 +2744,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2829,26 +2829,26 @@
         <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44439</v>
+        <v>44500</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44439</v>
+        <v>44500</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,61 +2949,143 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>44439</v>
+        <v>44469</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>60</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>59</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>59</v>
-      </c>
-      <c r="F63" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G63" s="1" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>58</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="G65" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2703,13 +2703,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2744,13 +2744,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F57" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2867,13 +2867,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F63" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_milho</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_milho.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1934,19 +1934,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_milho</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_milho.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>bcb_sgs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mercado_financeiro</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_selic_over</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,29 +2949,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>setor_externo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,102 +2990,20 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>59</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>44469</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>setor_externo</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>58</v>
-      </c>
-      <c r="F65" s="1" t="n">
-        <v>44500</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1782,7 +1782,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yahoo_nasdaq</t>
+          <t>yahoo_milho</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.csv</t>
+          <t>data/final/series/yahoo_milho.csv</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>yahoo_ouro</t>
+          <t>yahoo_nasdaq</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,19 +1852,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.csv</t>
+          <t>data/final/series/yahoo_nasdaq.csv</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ouro.xlsx</t>
+          <t>data/final/series/yahoo_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_brent</t>
+          <t>yahoo_ouro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ouro.csv</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yahoo_petroleo_wti</t>
+          <t>yahoo_petroleo_brent</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1934,19 +1934,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yahoo_ret_bova11</t>
+          <t>yahoo_petroleo_wti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1965,29 +1965,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.csv</t>
+          <t>data/final/series/yahoo_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
+          <t>data/final/series/yahoo_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yahoo_ret_dolar_real</t>
+          <t>yahoo_ret_bova11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2016,19 +2016,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
+          <t>data/final/series/yahoo_ret_bova11.csv</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_bova11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yahoo_ret_dow_jones</t>
+          <t>yahoo_ret_dolar_real</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
+          <t>data/final/series/yahoo_ret_dolar_real.csv</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
+          <t>data/final/series/yahoo_ret_dolar_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>yahoo_ret_euro_real</t>
+          <t>yahoo_ret_dow_jones</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2098,19 +2098,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.csv</t>
+          <t>data/final/series/yahoo_ret_dow_jones.csv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
+          <t>data/final/series/yahoo_ret_dow_jones.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yahoo_ret_ibovespa</t>
+          <t>yahoo_ret_euro_real</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2139,19 +2139,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
+          <t>data/final/series/yahoo_ret_euro_real.csv</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
+          <t>data/final/series/yahoo_ret_euro_real.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>yahoo_ret_ivvb11</t>
+          <t>yahoo_ret_ibovespa</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
+          <t>data/final/series/yahoo_ret_ibovespa.csv</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
+          <t>data/final/series/yahoo_ret_ibovespa.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yahoo_ret_nasdaq</t>
+          <t>yahoo_ret_ivvb11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2221,19 +2221,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
+          <t>data/final/series/yahoo_ret_ivvb11.csv</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
+          <t>data/final/series/yahoo_ret_ivvb11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yahoo_ret_ouro</t>
+          <t>yahoo_ret_milho</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.csv</t>
+          <t>data/final/series/yahoo_ret_milho.csv</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
+          <t>data/final/series/yahoo_ret_milho.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_brent</t>
+          <t>yahoo_ret_nasdaq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2303,19 +2303,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
+          <t>data/final/series/yahoo_ret_nasdaq.csv</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
+          <t>data/final/series/yahoo_ret_nasdaq.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yahoo_ret_petroleo_wti</t>
+          <t>yahoo_ret_ouro</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2344,19 +2344,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
+          <t>data/final/series/yahoo_ret_ouro.csv</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
+          <t>data/final/series/yahoo_ret_ouro.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yahoo_ret_smal11</t>
+          <t>yahoo_ret_petroleo_brent</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2385,19 +2385,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.csv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_brent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>yahoo_ret_soja</t>
+          <t>yahoo_ret_petroleo_wti</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.csv</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.csv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_petroleo_wti.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>yahoo_ret_sp500</t>
+          <t>yahoo_ret_smal11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2467,19 +2467,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.csv</t>
+          <t>data/final/series/yahoo_ret_smal11.csv</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
+          <t>data/final/series/yahoo_ret_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>yahoo_smal11</t>
+          <t>yahoo_ret_soja</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2498,29 +2498,29 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.csv</t>
+          <t>data/final/series/yahoo_ret_soja.csv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_smal11.xlsx</t>
+          <t>data/final/series/yahoo_ret_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>yahoo_soja</t>
+          <t>yahoo_ret_sp500</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2539,29 +2539,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.csv</t>
+          <t>data/final/series/yahoo_ret_sp500.csv</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_soja.xlsx</t>
+          <t>data/final/series/yahoo_ret_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yahoo_sp500</t>
+          <t>yahoo_smal11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2590,29 +2590,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.csv</t>
+          <t>data/final/series/yahoo_smal11.csv</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>data/final/series/yahoo_sp500.xlsx</t>
+          <t>data/final/series/yahoo_smal11.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>yahoo_soja</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2631,29 +2631,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/yahoo_soja.csv</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/yahoo_soja.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>yahoo_sp500</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>yahoo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>mercado_financeiro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2662,29 +2662,29 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/yahoo_sp500.csv</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/yahoo_sp500.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>bcb_sgs_cdi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2703,29 +2703,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,29 +2785,29 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,29 +2826,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2867,29 +2867,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2908,29 +2908,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,61 +2949,143 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>59</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
         <v>58</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F65" s="1" t="n">
         <v>44500</v>
       </c>
-      <c r="G63" s="1" t="n">
+      <c r="G65" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2684,17 +2684,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2703,39 +2703,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61</v>
+        <v>356</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>44469</v>
+        <v>35461</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/comexstat_comex_corrente_comercio_usd.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/comexstat_comex_corrente_comercio_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2744,39 +2744,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>60</v>
+        <v>356</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>44500</v>
+        <v>35461</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/comexstat_comex_exportacoes_fob_usd.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/comexstat_comex_exportacoes_fob_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2785,39 +2785,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>58</v>
+        <v>356</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>44500</v>
+        <v>35461</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/comexstat_comex_exportacoes_kg.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/comexstat_comex_exportacoes_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2826,39 +2826,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>356</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>44500</v>
+        <v>35461</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_cif_usd.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/comexstat_comex_importacoes_cif_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2867,39 +2867,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>356</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>44500</v>
+        <v>35461</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_fob_usd.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/comexstat_comex_importacoes_fob_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2908,39 +2908,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>356</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>44469</v>
+        <v>35461</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_frete_usd.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/comexstat_comex_importacoes_frete_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2949,39 +2949,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61</v>
+        <v>356</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>44469</v>
+        <v>35461</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_kg.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/comexstat_comex_importacoes_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2990,39 +2990,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>356</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44469</v>
+        <v>35461</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_seguro_usd.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/comexstat_comex_importacoes_seguro_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3031,61 +3031,430 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>59</v>
+        <v>356</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>44469</v>
+        <v>35461</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/comexstat_comex_saldo_comercial_usd.csv</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/comexstat_comex_saldo_comercial_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>bcb_sgs_cdi</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>61</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_cdi</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>60</v>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="G66" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>58</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_meta</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>60</v>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="G68" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>60</v>
+      </c>
+      <c r="F69" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="G69" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>bcb_sgs_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>59</v>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G70" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_meta</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>61</v>
+      </c>
+      <c r="F71" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G71" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>61</v>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G72" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>59</v>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G73" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>bcb_sgs</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
         <v>58</v>
       </c>
-      <c r="F65" s="1" t="n">
+      <c r="F74" s="1" t="n">
         <v>44500</v>
       </c>
-      <c r="G65" s="1" t="n">
+      <c r="G74" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>46265</v>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>46265</v>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>46265</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>46265</v>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>46265</v>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>46265</v>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>46265</v>
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>46265</v>
@@ -3012,7 +3012,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3031,39 +3031,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>35461</v>
+        <v>43861</v>
       </c>
       <c r="G64" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_saldo_comercial_usd.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd.csv</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_saldo_comercial_usd.xlsx</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3072,39 +3072,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>44469</v>
+        <v>43861</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg.csv</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_cdi</t>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3113,39 +3113,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd.csv</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
+          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3154,39 +3154,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg.csv</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3195,39 +3195,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd.csv</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3236,39 +3236,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>44500</v>
+        <v>43861</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg.csv</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3277,39 +3277,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>44469</v>
+        <v>44043</v>
       </c>
       <c r="G70" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd.csv</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
+          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3318,39 +3318,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>44469</v>
+        <v>44043</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg.csv</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
+          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>politica_monetaria</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3359,39 +3359,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>44469</v>
+        <v>43861</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd.csv</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>bcb_sgs</t>
+          <t>consolidada</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>outros</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3400,61 +3400,1619 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>44469</v>
+        <v>43861</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg.csv</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>80</v>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G74" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>80</v>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G75" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>80</v>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G76" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>80</v>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G77" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>76</v>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G78" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>76</v>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G79" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>80</v>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G80" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>80</v>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G81" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>79</v>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G82" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>79</v>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G83" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>80</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G84" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>80</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G85" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>5</v>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="G87" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>80</v>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G88" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>80</v>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G89" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>66</v>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>66</v>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>80</v>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>80</v>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>80</v>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>80</v>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>80</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G96" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>80</v>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G97" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>43</v>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>44196</v>
+      </c>
+      <c r="G98" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>43</v>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>44196</v>
+      </c>
+      <c r="G99" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>80</v>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G100" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>80</v>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G101" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>70</v>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G102" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd.csv</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>70</v>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G103" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg.csv</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>comexstat_comex_saldo_comercial_usd</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>consolidada</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>outros</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>80</v>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="G104" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_saldo_comercial_usd.csv</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>data/final/series/comexstat_comex_saldo_comercial_usd.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>bcb_sgs_cdi</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>61</v>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G105" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_cdi.csv</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_cdi.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_cdi</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>60</v>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="G106" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_cdi.csv</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_cdi.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>58</v>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="G107" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>60</v>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="G108" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>bcb_sgs_juros_credito_total</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>59</v>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G109" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>61</v>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G110" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>59</v>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G111" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>bcb_sgs</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
         <v>58</v>
       </c>
-      <c r="F74" s="1" t="n">
+      <c r="F112" s="1" t="n">
         <v>44500</v>
       </c>
-      <c r="G74" s="1" t="n">
+      <c r="G112" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>

--- a/data/final/documentacao/lista_series_individuais.xlsx
+++ b/data/final/documentacao/lista_series_individuais.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2684,7 +2684,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>comexstat_comex_corrente_comercio_usd</t>
+          <t>comexstat_acucares_cana_exp_fob</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2713,19 +2713,19 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_corrente_comercio_usd.csv</t>
+          <t>data/final/series/comexstat_acucares_cana_exp_fob.csv</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_corrente_comercio_usd.xlsx</t>
+          <t>data/final/series/comexstat_acucares_cana_exp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_fob_usd</t>
+          <t>comexstat_acucares_cana_exp_kg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_exportacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_acucares_cana_exp_kg.csv</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_exportacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_acucares_cana_exp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>comexstat_comex_exportacoes_kg</t>
+          <t>comexstat_acucares_cana_imp_fob</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>43861</v>
@@ -2795,19 +2795,19 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_acucares_cana_imp_fob.csv</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_exportacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_acucares_cana_imp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_cif_usd</t>
+          <t>comexstat_acucares_cana_imp_kg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>43861</v>
@@ -2836,19 +2836,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_cif_usd.csv</t>
+          <t>data/final/series/comexstat_acucares_cana_imp_kg.csv</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_cif_usd.xlsx</t>
+          <t>data/final/series/comexstat_acucares_cana_imp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_fob_usd</t>
+          <t>comexstat_cafe_nao_torrado_exp_fob</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2877,19 +2877,19 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_exp_fob.csv</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_exp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_frete_usd</t>
+          <t>comexstat_cafe_nao_torrado_exp_kg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2918,19 +2918,19 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_frete_usd.csv</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_exp_kg.csv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_frete_usd.xlsx</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_exp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_kg</t>
+          <t>comexstat_cafe_nao_torrado_imp_fob</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2949,29 +2949,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_imp_fob.csv</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_imp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>comexstat_comex_importacoes_seguro_usd</t>
+          <t>comexstat_cafe_nao_torrado_imp_kg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2990,29 +2990,29 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>43861</v>
+        <v>44043</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_seguro_usd.csv</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_imp_kg.csv</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_importacoes_seguro_usd.xlsx</t>
+          <t>data/final/series/comexstat_cafe_nao_torrado_imp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd</t>
+          <t>comexstat_carne_bovina_congelada_exp_fob</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3041,19 +3041,19 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_exp_fob.csv</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_exp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg</t>
+          <t>comexstat_carne_bovina_congelada_exp_kg</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3082,19 +3082,19 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_exp_kg.csv</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_exportacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_exp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd</t>
+          <t>comexstat_carne_bovina_congelada_imp_fob</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3123,19 +3123,19 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_imp_fob.csv</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_imp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg</t>
+          <t>comexstat_carne_bovina_congelada_imp_kg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3164,19 +3164,19 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_imp_kg.csv</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_02023000_carne_bovina_congelada_importacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_carne_bovina_congelada_imp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd</t>
+          <t>comexstat_celulose_nao_coniferas_exp_fob</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3205,19 +3205,19 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_exp_fob.csv</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_exp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg</t>
+          <t>comexstat_celulose_nao_coniferas_exp_kg</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3246,19 +3246,19 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_exp_kg.csv</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_exportacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_exp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd</t>
+          <t>comexstat_celulose_nao_coniferas_imp_fob</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3277,29 +3277,29 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_imp_fob.csv</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_imp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg</t>
+          <t>comexstat_celulose_nao_coniferas_imp_kg</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3318,29 +3318,29 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>44043</v>
+        <v>43861</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_imp_kg.csv</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_09011110_cafe_nao_torrado_importacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_celulose_nao_coniferas_imp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd</t>
+          <t>comexstat_comex_corrente_comercio_usd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3369,19 +3369,19 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_comex_corrente_comercio_usd.csv</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_comex_corrente_comercio_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg</t>
+          <t>comexstat_comex_exportacoes_fob_usd</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3410,19 +3410,19 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_comex_exportacoes_fob_usd.csv</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_exportacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_comex_exportacoes_fob_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_fob_usd</t>
+          <t>comexstat_comex_exportacoes_kg</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3451,19 +3451,19 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_comex_exportacoes_kg.csv</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_comex_exportacoes_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_cif_usd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3492,19 +3492,19 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_cif_usd.csv</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_10059010_milho_em_grao_importacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_comex_importacoes_cif_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd</t>
+          <t>comexstat_comex_importacoes_fob_usd</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3533,19 +3533,19 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_fob_usd.csv</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_comex_importacoes_fob_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg</t>
+          <t>comexstat_comex_importacoes_frete_usd</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3574,19 +3574,19 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_frete_usd.csv</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_exportacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_comex_importacoes_frete_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd</t>
+          <t>comexstat_comex_importacoes_kg</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F78" s="1" t="n">
         <v>43861</v>
@@ -3615,19 +3615,19 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_kg.csv</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_comex_importacoes_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg</t>
+          <t>comexstat_comex_importacoes_seguro_usd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F79" s="1" t="n">
         <v>43861</v>
@@ -3656,19 +3656,19 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_comex_importacoes_seguro_usd.csv</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_12019000_soja_exceto_semeadura_importacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_comex_importacoes_seguro_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_fob_usd</t>
+          <t>comexstat_comex_saldo_comercial_usd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3697,19 +3697,19 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_comex_saldo_comercial_usd.csv</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_comex_saldo_comercial_usd.xlsx</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg</t>
+          <t>comexstat_fuel_oil_exp_fob</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3738,19 +3738,19 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_fuel_oil_exp_fob.csv</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_exportacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_fuel_oil_exp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_fob_usd</t>
+          <t>comexstat_fuel_oil_exp_kg</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F82" s="1" t="n">
         <v>43861</v>
@@ -3779,19 +3779,19 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_fuel_oil_exp_kg.csv</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_fuel_oil_exp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg</t>
+          <t>comexstat_fuel_oil_imp_fob</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3810,29 +3810,29 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_fuel_oil_imp_fob.csv</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_17011400_acucares_cana_importacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_fuel_oil_imp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd</t>
+          <t>comexstat_fuel_oil_imp_kg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3851,29 +3851,29 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_fuel_oil_imp_kg.csv</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_fuel_oil_imp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg</t>
+          <t>comexstat_milho_em_grao_exp_fob</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3902,19 +3902,19 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_milho_em_grao_exp_fob.csv</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_exportacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_milho_em_grao_exp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd</t>
+          <t>comexstat_milho_em_grao_exp_kg</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3933,29 +3933,29 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="G86" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_milho_em_grao_exp_kg.csv</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_milho_em_grao_exp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg</t>
+          <t>comexstat_milho_em_grao_imp_fob</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3974,29 +3974,29 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="G87" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_milho_em_grao_imp_fob.csv</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_23040090_residuos_oleo_soja_importacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_milho_em_grao_imp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd</t>
+          <t>comexstat_milho_em_grao_imp_kg</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4025,19 +4025,19 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_milho_em_grao_imp_kg.csv</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_milho_em_grao_imp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_fob</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4066,19 +4066,19 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_exp_fob.csv</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_exportacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_exp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_exp_kg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F90" s="1" t="n">
         <v>43861</v>
@@ -4107,19 +4107,19 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_exp_kg.csv</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_exp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_fob</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4148,19 +4148,19 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_imp_fob.csv</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_26011100_minerio_ferro_nao_aglomerado_importacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_imp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd</t>
+          <t>comexstat_minerio_ferro_nao_aglomerado_imp_kg</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F92" s="1" t="n">
         <v>43861</v>
@@ -4189,19 +4189,19 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_imp_kg.csv</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_minerio_ferro_nao_aglomerado_imp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_fob</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4230,19 +4230,19 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_exp_fob.csv</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_exportacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_exp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd</t>
+          <t>comexstat_oleos_brutos_petroleo_exp_kg</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4271,19 +4271,19 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_exp_kg.csv</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_exp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_fob</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4312,19 +4312,19 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_imp_fob.csv</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27090010_oleos_brutos_petroleo_importacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_imp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_fob_usd</t>
+          <t>comexstat_oleos_brutos_petroleo_imp_kg</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4353,19 +4353,19 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_imp_kg.csv</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_oleos_brutos_petroleo_imp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg</t>
+          <t>comexstat_residuos_oleo_soja_exp_fob</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4394,19 +4394,19 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_residuos_oleo_soja_exp_fob.csv</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_exportacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_residuos_oleo_soja_exp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_fob_usd</t>
+          <t>comexstat_residuos_oleo_soja_exp_kg</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4425,29 +4425,29 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="F98" s="1" t="n">
-        <v>44196</v>
+        <v>43861</v>
       </c>
       <c r="G98" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_residuos_oleo_soja_exp_kg.csv</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_residuos_oleo_soja_exp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg</t>
+          <t>comexstat_residuos_oleo_soja_imp_fob</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4466,29 +4466,29 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="F99" s="1" t="n">
-        <v>44196</v>
+        <v>43890</v>
       </c>
       <c r="G99" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_residuos_oleo_soja_imp_fob.csv</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_27101922_fuel_oil_importacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_residuos_oleo_soja_imp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd</t>
+          <t>comexstat_residuos_oleo_soja_imp_kg</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4507,29 +4507,29 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="F100" s="1" t="n">
-        <v>43861</v>
+        <v>43890</v>
       </c>
       <c r="G100" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_residuos_oleo_soja_imp_kg.csv</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_residuos_oleo_soja_imp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg</t>
+          <t>comexstat_soja_exceto_semeadura_exp_fob</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4558,19 +4558,19 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg.csv</t>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_exp_fob.csv</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_exportacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_exp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd</t>
+          <t>comexstat_soja_exceto_semeadura_exp_kg</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F102" s="1" t="n">
         <v>43861</v>
@@ -4599,19 +4599,19 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd.csv</t>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_exp_kg.csv</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_fob_usd.xlsx</t>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_exp_kg.xlsx</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg</t>
+          <t>comexstat_soja_exceto_semeadura_imp_fob</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F103" s="1" t="n">
         <v>43861</v>
@@ -4640,19 +4640,19 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg.csv</t>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_imp_fob.csv</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_ncm_47032900_celulose_nao_coniferas_importacoes_kg.xlsx</t>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_imp_fob.xlsx</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>comexstat_comex_saldo_comercial_usd</t>
+          <t>comexstat_soja_exceto_semeadura_imp_kg</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4671,7 +4671,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F104" s="1" t="n">
         <v>43861</v>
@@ -4681,12 +4681,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_saldo_comercial_usd.csv</t>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_imp_kg.csv</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>data/final/series/comexstat_comex_saldo_comercial_usd.xlsx</t>
+          <t>data/final/series/comexstat_soja_exceto_semeadura_imp_kg.xlsx</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4845,19 +4845,19 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.csv</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>bcb_sgs_juros_credito_total</t>
+          <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4876,29 +4876,29 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F109" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="G109" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.csv</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
+          <t>data/final/series/bcb_sgs_dif_selic_over.xlsx</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4917,29 +4917,29 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F110" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G110" s="1" t="n">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.csv</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+          <t>data/final/series/bcb_sgs_juros_credito_total.xlsx</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>bcb_sgs_reservas_internacionais</t>
+          <t>bcb_sgs_selic_meta</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>setor_externo</t>
+          <t>politica_monetaria</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4958,61 +4958,143 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F111" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="G111" s="1" t="n">
-        <v>46234</v>
+        <v>46295</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+          <t>data/final/series/bcb_sgs_selic_meta.csv</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+          <t>data/final/series/bcb_sgs_selic_meta.xlsx</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>politica_monetaria</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>61</v>
+      </c>
+      <c r="F112" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G112" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.csv</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_selic_over.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>bcb_sgs_reservas_internacionais</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>bcb_sgs</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>setor_externo</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>59</v>
+      </c>
+      <c r="F113" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="G113" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.csv</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>data/final/series/bcb_sgs_reservas_internacionais.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>bcb_sgs</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>setor_externo</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>mensal</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>mensal</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
         <v>58</v>
       </c>
-      <c r="F112" s="1" t="n">
+      <c r="F114" s="1" t="n">
         <v>44500</v>
       </c>
-      <c r="G112" s="1" t="n">
+      <c r="G114" s="1" t="n">
         <v>46234</v>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.csv</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>data/final/series/bcb_sgs_var_pct_reservas_internacionais.xlsx</t>
         </is>
